--- a/tools/_out/airway_first_20261020/regen/stage/straight/DesignTable_6504_SW2.xlsx
+++ b/tools/_out/airway_first_20261020/regen/stage/straight/DesignTable_6504_SW2.xlsx
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2006 Side 1 ID = 1.312 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>[BRENNAN-CELL 2026-10-20: D1@BORE] Air-Way s100 only (double-pass 14 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2006 Side 1 ID = 1.312 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Brennan TFA catalog p17 table TFA-p017-t05 "MJ-FJS STRAIGHT" row 6504-24-24 col "B1 DRILL" = 1.312 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan] | MODEL: male JIC end: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); L13 = male tip to the nut face, L14 = male tip to the seat (L13-L14 = nut face to nose tip); body hex C, nut hex C3 (Air-Way); female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the body hex stops at the measured body-face position of the 6500 forged arm (ASSUMED for a straight body); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; bore step D1/D2 at the body-hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>D (1) printed 1.38 (D (2) 1.31); copied as printed</t>
+          <t>D (1) printed 1.38 (D (2) 1.31); copied as printed | 2026-10-20 D1@BORE = Brennan 1.312 (Air-Way 1.38 cannot be built: Air-Way bore 1.38 &gt;= the -24 JIC tip dia 1.381 (generator BLOCKED))</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
